--- a/artfynd/A 6878-2021 artfynd.xlsx
+++ b/artfynd/A 6878-2021 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Robert Flygare, Stefan Andersson</t>
+          <t>Stefan Andersson, Robert Flygare, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 6878-2021 artfynd.xlsx
+++ b/artfynd/A 6878-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117585225</v>
       </c>
       <c r="B2" t="n">
-        <v>90648</v>
+        <v>90650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Robert Flygare, Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd, Robert Flygare, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
